--- a/lesson3/answer1.xlsx
+++ b/lesson3/answer1.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Documents</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -542,8 +542,10 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
-        <v>303064</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
       </c>
       <c r="D2" t="n">
         <v>301778</v>
@@ -604,8 +606,10 @@
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>184851</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
       </c>
       <c r="D3" t="n">
         <v>181106</v>
@@ -672,8 +676,10 @@
       <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>60257</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
       </c>
       <c r="D4" t="n">
         <v>58589</v>
@@ -740,8 +746,10 @@
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
-        <v>52780</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
       </c>
       <c r="D5" t="n">
         <v>52281</v>
@@ -802,8 +810,10 @@
       <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
-        <v>47141</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
       </c>
       <c r="D6" t="n">
         <v>45928</v>
@@ -864,8 +874,10 @@
       <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
-        <v>42343</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
       </c>
       <c r="D7" t="n">
         <v>41464</v>
@@ -932,8 +944,10 @@
       <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
-        <v>39424</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
       </c>
       <c r="D8" t="n">
         <v>39189</v>
@@ -1000,8 +1014,10 @@
       <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
-        <v>35588</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
       </c>
       <c r="D9" t="n">
         <v>34940</v>
@@ -1068,8 +1084,10 @@
       <c r="B10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
-        <v>31260</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
       </c>
       <c r="D10" t="n">
         <v>29959</v>
@@ -1130,8 +1148,10 @@
       <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
-        <v>31200</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
       </c>
       <c r="D11" t="n">
         <v>30949</v>
@@ -1198,8 +1218,10 @@
       <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
-        <v>26848</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
       </c>
       <c r="D12" t="n">
         <v>26320</v>
@@ -1260,8 +1282,10 @@
       <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
-        <v>25481</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
       </c>
       <c r="D13" t="n">
         <v>25204</v>
@@ -1322,8 +1346,10 @@
       <c r="B14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
-        <v>24969</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
       </c>
       <c r="D14" t="n">
         <v>24505</v>
@@ -1384,8 +1410,10 @@
       <c r="B15" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="n">
-        <v>23110</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
       </c>
       <c r="D15" t="n">
         <v>22762</v>
@@ -1452,8 +1480,10 @@
       <c r="B16" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="n">
-        <v>22803</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
       </c>
       <c r="D16" t="n">
         <v>22276</v>

--- a/lesson3/answer1.xlsx
+++ b/lesson3/answer1.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
@@ -436,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Documents</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -536,16 +541,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
+      <c r="C2" t="n">
+        <v>303064</v>
       </c>
       <c r="D2" t="n">
         <v>301778</v>
@@ -600,16 +605,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
+      <c r="C3" t="n">
+        <v>184851</v>
       </c>
       <c r="D3" t="n">
         <v>181106</v>
@@ -670,16 +675,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
+      <c r="C4" t="n">
+        <v>60257</v>
       </c>
       <c r="D4" t="n">
         <v>58589</v>
@@ -740,16 +745,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+      <c r="C5" t="n">
+        <v>52780</v>
       </c>
       <c r="D5" t="n">
         <v>52281</v>
@@ -804,16 +809,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
+      <c r="C6" t="n">
+        <v>47141</v>
       </c>
       <c r="D6" t="n">
         <v>45928</v>
@@ -868,16 +873,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
       </c>
       <c r="B7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+      <c r="C7" t="n">
+        <v>42343</v>
       </c>
       <c r="D7" t="n">
         <v>41464</v>
@@ -938,16 +943,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Russian Federation</t>
+        </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Russian Federation</t>
-        </is>
+      <c r="C8" t="n">
+        <v>39424</v>
       </c>
       <c r="D8" t="n">
         <v>39189</v>
@@ -1008,16 +1013,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
       </c>
       <c r="B9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+      <c r="C9" t="n">
+        <v>35588</v>
       </c>
       <c r="D9" t="n">
         <v>34940</v>
@@ -1078,16 +1083,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
       </c>
       <c r="B10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
+      <c r="C10" t="n">
+        <v>31260</v>
       </c>
       <c r="D10" t="n">
         <v>29959</v>
@@ -1142,16 +1147,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
+      <c r="C11" t="n">
+        <v>31200</v>
       </c>
       <c r="D11" t="n">
         <v>30949</v>
@@ -1212,16 +1217,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
       </c>
       <c r="B12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+      <c r="C12" t="n">
+        <v>26848</v>
       </c>
       <c r="D12" t="n">
         <v>26320</v>
@@ -1276,16 +1281,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
+      <c r="C13" t="n">
+        <v>25481</v>
       </c>
       <c r="D13" t="n">
         <v>25204</v>
@@ -1340,16 +1345,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
       </c>
       <c r="B14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+      <c r="C14" t="n">
+        <v>24969</v>
       </c>
       <c r="D14" t="n">
         <v>24505</v>
@@ -1404,16 +1409,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+      <c r="C15" t="n">
+        <v>23110</v>
       </c>
       <c r="D15" t="n">
         <v>22762</v>
@@ -1474,16 +1479,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
       </c>
       <c r="B16" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+      <c r="C16" t="n">
+        <v>22803</v>
       </c>
       <c r="D16" t="n">
         <v>22276</v>

--- a/lesson3/answer1.xlsx
+++ b/lesson3/answer1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\data_science_camp\lesson3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BC679E-C136-4E51-8D85-95E61AE460CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BB2E11-4807-4BE0-99A6-E3DBD9D74CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="276" yWindow="2184" windowWidth="8556" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="108" yWindow="1836" windowWidth="12108" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -496,6 +496,8 @@
   <dimension ref="A1:V16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
     <col min="6" max="6" width="14.33203125" customWidth="1"/>
     <col min="7" max="7" width="20.21875" customWidth="1"/>

--- a/lesson3/answer1.xlsx
+++ b/lesson3/answer1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\data_science_camp\lesson3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49BB2E11-4807-4BE0-99A6-E3DBD9D74CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F080D2A1-C84F-4FCC-9850-5C998BCA0E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="108" yWindow="1836" windowWidth="12108" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="3924" yWindow="5268" windowWidth="17400" windowHeight="7164" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -496,6 +496,7 @@
   <dimension ref="A1:V16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" customWidth="1"/>
